--- a/src/test/resources/uom.xlsx
+++ b/src/test/resources/uom.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\comag\Documents\Projects\shopeesalescoverter\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FEF6B6-50FC-4B99-84F4-9F588015AEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1EB5B0-F53F-4AE7-8FDA-53A493B7CE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="49">
   <si>
     <t>IM_ITEMNO</t>
   </si>
@@ -58,6 +69,120 @@
   </si>
   <si>
     <t>mug</t>
+  </si>
+  <si>
+    <t>Crunch Roll Vanilla</t>
+  </si>
+  <si>
+    <t>Chip Bulk Potato</t>
+  </si>
+  <si>
+    <t>Chip Bulk Green Pea</t>
+  </si>
+  <si>
+    <t>Checkers Classic</t>
+  </si>
+  <si>
+    <t>Cookies Creeam 20pcs</t>
+  </si>
+  <si>
+    <t>Peanut Coated Chocolate 100pcs</t>
+  </si>
+  <si>
+    <t>Dried Fruit 2kg</t>
+  </si>
+  <si>
+    <t>Instant Powder Blueberry</t>
+  </si>
+  <si>
+    <t>Instant Powder Grape</t>
+  </si>
+  <si>
+    <t>Instant Powder Strawberry</t>
+  </si>
+  <si>
+    <t>Instant Powder Mango</t>
+  </si>
+  <si>
+    <t>Instant Powder Blackcurrant</t>
+  </si>
+  <si>
+    <t>Instant Powder Blackberry</t>
+  </si>
+  <si>
+    <t>Chocolate Bean 50pcs</t>
+  </si>
+  <si>
+    <t>Bubble Water Mini</t>
+  </si>
+  <si>
+    <t>Peanut Candy 1kg</t>
+  </si>
+  <si>
+    <t>Jelly Grab Shape 50pcs</t>
+  </si>
+  <si>
+    <t>Thai Snack Pop Can</t>
+  </si>
+  <si>
+    <t>Powder Fruit Candy</t>
+  </si>
+  <si>
+    <t>Jelly Cat Paw Shape</t>
+  </si>
+  <si>
+    <t>Gumm Bulk Egg</t>
+  </si>
+  <si>
+    <t>Gummy Bulk Teeth</t>
+  </si>
+  <si>
+    <t>Gummy Bulk Dolphin</t>
+  </si>
+  <si>
+    <t>Gummy Bulk Ice Cream</t>
+  </si>
+  <si>
+    <t>Whistle</t>
+  </si>
+  <si>
+    <t>Crunch Roll Chocolate</t>
+  </si>
+  <si>
+    <t>Keropok Cheese</t>
+  </si>
+  <si>
+    <t>Keropok BBQ</t>
+  </si>
+  <si>
+    <t>Keropok Spicy</t>
+  </si>
+  <si>
+    <t>Chocolate Classic</t>
+  </si>
+  <si>
+    <t>Sour Plum</t>
+  </si>
+  <si>
+    <t>Lollipop 200pcs Classic</t>
+  </si>
+  <si>
+    <t>Nougat Cocoa</t>
+  </si>
+  <si>
+    <t>Nougat Strawberry</t>
+  </si>
+  <si>
+    <t>Nougat Blueberry</t>
+  </si>
+  <si>
+    <t>Nougat Mango</t>
+  </si>
+  <si>
+    <t>Kacang Tumbuk</t>
+  </si>
+  <si>
+    <t>Sour Candy Blueberry</t>
   </si>
 </sst>
 </file>
@@ -375,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -473,6 +598,652 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>9557207</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>9557208</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>7.2799999999999994</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>9557209</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>7.2799999999999994</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>9557210</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>6.7899999999999991</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9557211</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>5.46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9557212</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>8.26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>9557213</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>29.679999999999996</v>
+      </c>
+      <c r="D12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>9557214</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>6.58</v>
+      </c>
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>9557215</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>6.58</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>9557216</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>6.58</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>9557217</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>6.58</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>9557218</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>6.58</v>
+      </c>
+      <c r="D17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>9557219</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>6.58</v>
+      </c>
+      <c r="D18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>9557220</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>8.33</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>9557221</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>6.72</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>9557222</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21">
+        <v>12.25</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>9557223</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22">
+        <v>9.4499999999999993</v>
+      </c>
+      <c r="D22" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>9557224</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23">
+        <v>8.33</v>
+      </c>
+      <c r="D23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>9557225</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24">
+        <v>4.55</v>
+      </c>
+      <c r="D24" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>9557226</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25">
+        <v>9.31</v>
+      </c>
+      <c r="D25" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>9557227</v>
+      </c>
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26">
+        <v>13.51</v>
+      </c>
+      <c r="D26" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>9557228</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27">
+        <v>13.51</v>
+      </c>
+      <c r="D27" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>9557229</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28">
+        <v>13.51</v>
+      </c>
+      <c r="D28" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>9557230</v>
+      </c>
+      <c r="B29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29">
+        <v>13.51</v>
+      </c>
+      <c r="D29" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>9557231</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30">
+        <v>6.02</v>
+      </c>
+      <c r="D30" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>9557232</v>
+      </c>
+      <c r="B31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31">
+        <v>6.51</v>
+      </c>
+      <c r="D31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>9557233</v>
+      </c>
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32">
+        <v>12.95</v>
+      </c>
+      <c r="D32" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>9557234</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33">
+        <v>12.95</v>
+      </c>
+      <c r="D33" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>9557235</v>
+      </c>
+      <c r="B34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34">
+        <v>12.95</v>
+      </c>
+      <c r="D34" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>9557236</v>
+      </c>
+      <c r="B35" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35">
+        <v>5.9499999999999993</v>
+      </c>
+      <c r="D35" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>9557237</v>
+      </c>
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36">
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="D36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>9557238</v>
+      </c>
+      <c r="B37" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37">
+        <v>13.649999999999999</v>
+      </c>
+      <c r="D37" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>9557239</v>
+      </c>
+      <c r="B38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38">
+        <v>4.55</v>
+      </c>
+      <c r="D38" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>9557240</v>
+      </c>
+      <c r="B39" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39">
+        <v>4.55</v>
+      </c>
+      <c r="D39" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>9557241</v>
+      </c>
+      <c r="B40" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40">
+        <v>4.55</v>
+      </c>
+      <c r="D40" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>9557242</v>
+      </c>
+      <c r="B41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41">
+        <v>4.55</v>
+      </c>
+      <c r="D41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>9557243</v>
+      </c>
+      <c r="B42" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42">
+        <v>14.629999999999997</v>
+      </c>
+      <c r="D42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>9557244</v>
+      </c>
+      <c r="B43" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43">
+        <v>19.25</v>
+      </c>
+      <c r="D43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
